--- a/PageObjectiveModel/src/test/java/Resources/loginData.xlsx
+++ b/PageObjectiveModel/src/test/java/Resources/loginData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\JavaAuto\Hoc_Selenium\PageObjectiveModel\src\test\java\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCA327A-7B8A-44BE-A20E-7D8E81E24622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EEEE796-2754-4505-AA8F-DE0B23BC1156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13905" yWindow="1620" windowWidth="14595" windowHeight="13860" xr2:uid="{E5B78084-5252-439A-AC0D-7DEF6C3FEAF3}"/>
+    <workbookView xWindow="21240" yWindow="5625" windowWidth="14595" windowHeight="13860" xr2:uid="{082849E7-C696-47DA-AA79-836DBF6912DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,13 +45,13 @@
     <t>expectedResult</t>
   </si>
   <si>
-    <t>Tri</t>
-  </si>
-  <si>
     <t>Admin</t>
   </si>
   <si>
     <t>admin123</t>
+  </si>
+  <si>
+    <t>wrongpass</t>
   </si>
 </sst>
 </file>
@@ -402,14 +402,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56AE435-0A24-4828-BC3B-CBCBCF02B19E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC88EEDD-9C6F-4ABA-83C4-3960D6BC425D}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -424,10 +419,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -446,7 +441,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -454,7 +449,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
